--- a/JsonConverter/ExcelFiles/LevelUpRewardData.xlsx
+++ b/JsonConverter/ExcelFiles/LevelUpRewardData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -82,9 +82,6 @@
     <t>최대체력이 10%증가합니다.</t>
   </si>
   <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
     <t>Percent</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
   </si>
   <si>
     <t>이동속도가 1 증가합니다.</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
   </si>
   <si>
     <t>Flat</t>
@@ -118,9 +112,6 @@
     <t>공격력이 5 증가합니다.</t>
   </si>
   <si>
-    <t>Attack</t>
-  </si>
-  <si>
     <t>Reward/Icon2[Reward2_0]</t>
   </si>
   <si>
@@ -131,9 +122,6 @@
   </si>
   <si>
     <t>아이템 자석의 범위가 10% 증가합니다.</t>
-  </si>
-  <si>
-    <t>MagnetRange</t>
   </si>
   <si>
     <t>Reward/Icon[RewardIcon_7]</t>
@@ -148,9 +136,6 @@
     <t>방어력이 5 증가합니다.</t>
   </si>
   <si>
-    <t>Armor</t>
-  </si>
-  <si>
     <t>Reward/Icon3[RewardIcon3_0]</t>
   </si>
   <si>
@@ -161,9 +146,6 @@
   </si>
   <si>
     <t>크리티컬 확률이 5%증가합니다.</t>
-  </si>
-  <si>
-    <t>CriticalPercent</t>
   </si>
   <si>
     <t>Reward/Icon[RewardIcon_5]</t>
@@ -241,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -249,19 +231,13 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -270,7 +246,7 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,19 +529,19 @@
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="3"/>
@@ -590,75 +566,75 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="F4" s="3">
         <v>10.0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="3">
         <v>5.0</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>25</v>
+      <c r="H4" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -682,29 +658,29 @@
       <c r="AB4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>29</v>
+      <c r="F5" s="6">
+        <v>10.0</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="G5" s="3">
         <v>5.0</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>31</v>
+      <c r="H5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -728,29 +704,29 @@
       <c r="AB5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
+      <c r="D6" s="6">
+        <v>3.0</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="F6" s="3">
         <v>5.0</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="3">
         <v>3.0</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>36</v>
+      <c r="H6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -774,29 +750,29 @@
       <c r="AB6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>37</v>
+      <c r="A7" s="1" t="s">
+        <v>34</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
+      <c r="D7" s="6">
+        <v>4.0</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>24</v>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="3">
         <v>10.0</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="3">
         <v>3.0</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>41</v>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -820,29 +796,29 @@
       <c r="AB7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
+      <c r="A8" s="1" t="s">
+        <v>38</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>43</v>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>44</v>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="D8" s="6">
         <v>5.0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="3">
         <v>3.0</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>46</v>
+      <c r="H8" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -866,29 +842,29 @@
       <c r="AB8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
+      <c r="A9" s="1" t="s">
+        <v>42</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>48</v>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>49</v>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>50</v>
+      <c r="D9" s="6">
+        <v>6.0</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="3">
         <v>5.0</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="3">
         <v>5.0</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>51</v>
+      <c r="H9" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
